--- a/Hoàng/2025/T5/ĐẢNG UỶ UỶ BAN NHÂN DÂN THÀNH PHỐ ĐÀ NẴNG (63-2025)/DS, DM - ĐẢNG ỦY ỦY BAN NHÂN THÀNH PHỐ ĐÀ NẴNG 2025.xlsx
+++ b/Hoàng/2025/T5/ĐẢNG UỶ UỶ BAN NHÂN DÂN THÀNH PHỐ ĐÀ NẴNG (63-2025)/DS, DM - ĐẢNG ỦY ỦY BAN NHÂN THÀNH PHỐ ĐÀ NẴNG 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA-TN\Hoàng\2025\ĐẢNG UỶ UỶ BAN NHÂN DÂN THÀNH PHỐ ĐÀ NẴNG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\ĐẢNG UỶ UỶ BAN NHÂN DÂN THÀNH PHỐ ĐÀ NẴNG (63-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25B7CF2-AB0F-4CA2-B274-C73EA58E1D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FBEB1E-BEC3-4B05-A0A7-3251FAD714A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DS" sheetId="3" r:id="rId1"/>
@@ -444,20 +444,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -488,28 +488,28 @@
     </font>
     <font>
       <sz val="13"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri Light"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri Light"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri Light"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri Light"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
@@ -629,7 +629,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -690,26 +690,26 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -993,17 +993,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{016C6682-CEF2-4940-9A5A-EC403C649ACD}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.08203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="17">
         <v>1</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <v>2</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <v>3</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <v>4</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <v>5</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <v>6</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>7</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>8</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>9</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>10</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>11</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>12</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>13</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>14</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <v>15</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>16</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <v>17</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <v>18</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <v>19</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <v>20</v>
       </c>
@@ -1437,23 +1437,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE017E9E-0BCC-4191-B4F6-97E043849464}">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.25" customWidth="1"/>
-    <col min="3" max="3" width="33.75" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" customWidth="1"/>
     <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="21"/>
+      <c r="C1" s="25"/>
       <c r="D1" s="5" t="s">
         <v>68</v>
       </c>
@@ -1461,73 +1461,73 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="24">
+    <row r="2" spans="1:5" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="20">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="22" t="s">
         <v>70</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="26">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="33" x14ac:dyDescent="0.3">
-      <c r="A3" s="24"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="25"/>
+      <c r="E2" s="23">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="22"/>
       <c r="D3" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="26"/>
-    </row>
-    <row r="4" spans="1:5" ht="33" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="25"/>
+      <c r="E3" s="23"/>
+    </row>
+    <row r="4" spans="1:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
       <c r="D4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="26"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="25"/>
+      <c r="E4" s="23"/>
+    </row>
+    <row r="5" spans="1:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="22"/>
       <c r="D5" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="26"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="24"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="25"/>
+      <c r="E5" s="23"/>
+    </row>
+    <row r="6" spans="1:5" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
       <c r="D6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="26"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="25"/>
+      <c r="E6" s="23"/>
+    </row>
+    <row r="7" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
       <c r="D7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="26"/>
-    </row>
-    <row r="8" spans="1:5" ht="33" x14ac:dyDescent="0.35">
+      <c r="E7" s="23"/>
+    </row>
+    <row r="8" spans="1:5" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>2</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>77</v>
       </c>
       <c r="C8" s="8" t="s">
@@ -1540,11 +1540,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="51.75" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>3</v>
       </c>
-      <c r="B9" s="22"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="7" t="s">
         <v>80</v>
       </c>
@@ -1555,11 +1555,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="66" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="69" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>4</v>
       </c>
-      <c r="B10" s="22"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="7" t="s">
         <v>82</v>
       </c>
@@ -1570,11 +1570,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="51.75" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>5</v>
       </c>
-      <c r="B11" s="22"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="7" t="s">
         <v>84</v>
       </c>
@@ -1585,11 +1585,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="66" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="69" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>6</v>
       </c>
-      <c r="B12" s="22"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="7" t="s">
         <v>86</v>
       </c>
@@ -1600,11 +1600,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="51.75" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>7</v>
       </c>
-      <c r="B13" s="22"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="7" t="s">
         <v>88</v>
       </c>
@@ -1613,11 +1613,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>8</v>
       </c>
-      <c r="B14" s="22"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="7" t="s">
         <v>89</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="103.5" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>9</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="66" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="86.25" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>10</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="51.75" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>11</v>
       </c>
@@ -1679,11 +1679,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="51.75" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>12</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="21" t="s">
         <v>100</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -1696,11 +1696,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="51.75" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>13</v>
       </c>
-      <c r="B19" s="22"/>
+      <c r="B19" s="21"/>
       <c r="C19" s="10" t="s">
         <v>103</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="69" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>14</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="51.75" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>16</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="69" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>17</v>
       </c>
@@ -1762,11 +1762,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>18</v>
       </c>
-      <c r="B23" s="22"/>
+      <c r="B23" s="21"/>
       <c r="C23" s="10" t="s">
         <v>113</v>
       </c>
@@ -1777,11 +1777,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>19</v>
       </c>
-      <c r="B24" s="22"/>
+      <c r="B24" s="21"/>
       <c r="C24" s="11" t="s">
         <v>115</v>
       </c>
@@ -1792,11 +1792,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="33" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="51.75" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>20</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="26" t="s">
         <v>117</v>
       </c>
       <c r="C25" s="12" t="s">
@@ -1809,11 +1809,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="33" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="51.75" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>21</v>
       </c>
-      <c r="B26" s="23"/>
+      <c r="B26" s="26"/>
       <c r="C26" s="12" t="s">
         <v>120</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="51.75" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>22</v>
       </c>
@@ -1839,11 +1839,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>23</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="21" t="s">
         <v>124</v>
       </c>
       <c r="C28" s="11" t="s">
@@ -1856,11 +1856,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>24</v>
       </c>
-      <c r="B29" s="22"/>
+      <c r="B29" s="21"/>
       <c r="C29" s="11" t="s">
         <v>126</v>
       </c>
@@ -1871,11 +1871,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="51.75" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>25</v>
       </c>
-      <c r="B30" s="22"/>
+      <c r="B30" s="21"/>
       <c r="C30" s="11" t="s">
         <v>128</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>26</v>
       </c>
@@ -1903,16 +1903,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B8:B14"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B26"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="B2:B7"/>
     <mergeCell ref="C2:C7"/>
     <mergeCell ref="B28:B30"/>
     <mergeCell ref="E2:E7"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B8:B14"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B25:B26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
